--- a/Pruebas calificadas/COLEGIO MIRAVALLE (IED)-303_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO MIRAVALLE (IED)-303_Ajustado_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -759,7 +755,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -950,11 +946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -962,7 +954,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1145,11 +1137,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -1157,7 +1145,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1348,11 +1336,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -1360,7 +1344,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1551,11 +1535,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -1563,7 +1543,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1750,11 +1730,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -1762,7 +1738,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1953,11 +1929,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -1965,7 +1937,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2156,11 +2128,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -2168,7 +2136,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2355,11 +2323,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -2367,7 +2331,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2558,11 +2522,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -2570,7 +2530,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2761,11 +2721,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -2773,7 +2729,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2964,11 +2920,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -2976,7 +2928,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3167,11 +3119,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -3179,7 +3127,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3370,11 +3318,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -3382,7 +3326,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3565,11 +3509,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -3577,7 +3517,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3768,11 +3708,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -3780,7 +3716,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3955,11 +3891,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -3967,7 +3899,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4158,11 +4090,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -4170,7 +4098,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4361,11 +4289,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -4373,7 +4297,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4564,11 +4488,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -4576,7 +4496,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4767,11 +4687,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -4779,7 +4695,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4970,11 +4886,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -4982,7 +4894,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5173,11 +5085,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -5185,7 +5093,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5372,11 +5280,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -5384,7 +5288,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5575,11 +5479,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -5587,7 +5487,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5778,11 +5678,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -5790,7 +5686,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -5981,11 +5877,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -5993,7 +5885,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6184,11 +6076,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -6196,7 +6084,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6387,11 +6275,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -6399,7 +6283,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6590,11 +6474,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -6602,7 +6482,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6793,11 +6673,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -6805,7 +6681,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -6996,11 +6872,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -7008,7 +6880,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7199,11 +7071,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -7211,7 +7079,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7386,11 +7254,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -7398,7 +7262,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7589,11 +7453,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -7601,7 +7461,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7792,11 +7652,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -7804,7 +7660,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -7995,11 +7851,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -8007,7 +7859,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8198,11 +8050,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -8210,7 +8058,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8401,11 +8249,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -8413,7 +8257,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8592,11 +8436,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -8604,7 +8444,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8783,11 +8623,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -8795,7 +8631,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -8986,11 +8822,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -8998,7 +8830,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9189,11 +9021,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -9201,7 +9029,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9392,11 +9220,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -9404,7 +9228,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9595,11 +9419,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -9607,7 +9427,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9790,11 +9610,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -9802,7 +9618,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -9993,11 +9809,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -10005,7 +9817,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10196,11 +10008,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -10208,7 +10016,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10399,11 +10207,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -10411,7 +10215,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -10594,11 +10398,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -10606,7 +10406,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -10797,11 +10597,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -10809,7 +10605,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -11000,11 +10796,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -11012,7 +10804,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11203,11 +10995,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -11215,7 +11003,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11406,11 +11194,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -11418,7 +11202,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11609,11 +11393,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -11621,7 +11401,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11812,11 +11592,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -11824,7 +11600,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -12015,11 +11791,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -12027,7 +11799,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -12214,11 +11986,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -12226,7 +11994,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -12413,11 +12181,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -12425,7 +12189,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -12616,11 +12380,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -12628,7 +12388,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -12819,11 +12579,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -12831,7 +12587,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -13022,11 +12778,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -13034,7 +12786,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -13225,11 +12977,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -13237,7 +12985,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -13428,11 +13176,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -13440,7 +13184,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -13631,11 +13375,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -13643,7 +13383,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -13834,11 +13574,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -13846,7 +13582,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -14037,11 +13773,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -14049,7 +13781,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -14240,11 +13972,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -14252,7 +13980,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -14443,11 +14171,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -14455,7 +14179,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -14646,11 +14370,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -14658,7 +14378,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -14849,11 +14569,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -14861,7 +14577,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -15052,11 +14768,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -15064,7 +14776,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
